--- a/daily_matches/job_matches_2026-08-26.xlsx
+++ b/daily_matches/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, Data Management</t>
+          <t>Senior Software Engineer (Revenue)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Zuora</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Redshift, BigQuery, Synapse</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed5484e209306fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (Generative AI)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, PyTorch, Kubernetes, Terraform</t>
+          <t>RAG, Redshift, BigQuery, Kubernetes, Terraform, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e737ef5e0687a08b</t>
+          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>HARVEY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+          <t>RAG, Redshift, BigQuery, Kubernetes, Terraform, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adde54c1dfeeb1f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior eCommerce Engineer - Sarnova - Remote</t>
+          <t>C Sharp / .Net Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sarnova HC, LLC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaa7602c43284c05</t>
+          <t>https://www.indeed.com/viewjob?jk=a69f43ffb892e4d2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COSMOS - Postdoctoral Fellow II</t>
+          <t>Senior Software Engineer – TeamUp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>University of Arkansas</t>
+          <t>DaySmart Software</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, spaCy, NLTK, Gensim, Git, Matplotlib, Seaborn, Python</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, Git, Kafka, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b04aa6be5749603e</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2c2e30cced07c2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer — Translational Data Products</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, S3, Glue, Docker, CI/CD, GitHub Actions, Git, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4b1b272c14fcd4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, S3, Redshift, CI/CD, Jenkins, Git, Redshift, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=755efb0ab764a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer, AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>AI Engineer, CI/CD, GitHub Actions, Git, MySQL, MongoDB, NoSQL, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65de9dfcfa9f1fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=b58f00f5a0707436</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Databricks, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5f309ea3930e00</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>AI Agentic Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadff99f545dd065</t>
+          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Capital Insights</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Evolve vacation rentals</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, SQL, R</t>
+          <t>RAG, S3, EC2, Data Lake, CI/CD, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905399d801060878</t>
+          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f566575cdfa59d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c42ac46bdb574412</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ACT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Iowa City, IA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a83b678e92901eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5d2f27d51c055ab2</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bfe535ba3af5985</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1f235e7c67f5d7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lanngchain Engineer</t>
+          <t>Senior Software Test Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40f34d58110614ae</t>
+          <t>https://www.indeed.com/viewjob?jk=75b2df47a2c7f568</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Developer / Software Engineer – Backend &amp; Data Focus</t>
+          <t>Senior Python-AI Engineer Agentic Systems</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, Snowflake, Databricks, Python, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Git, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c4e1b44fb3c87</t>
+          <t>https://www.indeed.com/viewjob?jk=5c462696a046fe90</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Software Engineer Full Stack / Backend II (Full-Time) - United States</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f801b20e257baf3</t>
+          <t>https://www.indeed.com/viewjob?jk=a887578c9e44d7e3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Security Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aspirion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Newark, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ed16b6d896ab50</t>
+          <t>https://www.indeed.com/viewjob?jk=c77964bcc3b4d3b9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Specialist - Quality Engineering</t>
+          <t>Senior Data Scientist - Supply Chain Operations</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, FastAPI, Docker, Kubernetes, Python, R</t>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f563820255a5e3e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5cfbc33620816a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Specialist - Quality Engineering</t>
+          <t>Sr Software Engineer in Test</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, FastAPI, Docker, Kubernetes, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42024388869c4c1</t>
+          <t>https://www.indeed.com/viewjob?jk=aebd55b3221a1a76</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer, Data &amp; AI Platform</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SimplePractice</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, PyTorch, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b00d7042d542536</t>
+          <t>https://www.indeed.com/viewjob?jk=a4a55006fc9efc58</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Applied AI ML Associate</t>
+          <t>Senior Software Engineer, Power Platform, Copilot Studio, Azure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Python, R, Java, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f24407e0d926238</t>
+          <t>https://www.indeed.com/viewjob?jk=6e841a5a1c02dc01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II-SQL (T-SQL/PL-SQL), Azure, Spark/Hadoop</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Git, Hadoop, Power BI, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b643d276050a234</t>
+          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C&amp;W Services</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Git, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27bf2b040cf33973</t>
+          <t>https://www.indeed.com/viewjob?jk=546d4bc55a750071</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer, Analytics</t>
+          <t>SDET Web Automation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,322 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ab440c93bda25b</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Analytics</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>AES Corporation</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Louisville, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abf2c8858d372138</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Analytics</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>AES Corporation</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08a226425e0c1a0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior .NET Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Red Hawk Technologies</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, Kubernetes, Git, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1d191627864707</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Data Scientist III</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3a575f874a092d</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Software Engineer (Test Automation)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>iManage</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2cbb07af073cc27</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>BWE</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e98da6d39c387218</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Mobile App Developer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>AAA The Auto Club Group</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>MI, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, S3, CI/CD, Terraform, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00bf9f4912ad99df</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Sr Data Scientist - AI Program Office – Division of Information Technology</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Board of Governors of the Federal Reserve System</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5762cc90a1b1abf9</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Analyst, AI</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Coeur Mining, Inc.</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Cortex, Snowflake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e18a9a82d73c819</t>
+          <t>https://www.indeed.com/viewjob?jk=da2a4ffcbfc48ea3</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-26.xlsx
+++ b/daily_matches/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Revenue)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zuora</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, MySQL, MongoDB, NoSQL, Python</t>
+          <t>LangChain, RAG, Pinecone, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d66762c1438bbeb</t>
+          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Associate - Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Kubernetes, Terraform, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edcca601c37b3df4</t>
+          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior QA Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HARVEY</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Kubernetes, Terraform, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Quicksight</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c6800ab3996b5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0e151be0bbb235</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C Sharp / .Net Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Electric Power Engineers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69f43ffb892e4d2</t>
+          <t>https://www.indeed.com/viewjob?jk=1b3ddf4250ef85b5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – TeamUp</t>
+          <t>Senior Data AI Engineer - Java</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DaySmart Software</t>
+          <t>CNA Insurance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, Git, Kafka, MySQL, Python, SQL</t>
+          <t>AI Engineer, RAG, BigQuery, Data Lake, Dataflow, CI/CD, BigQuery, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2c2e30cced07c2</t>
+          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — Translational Data Products</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Benda Infotech</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, S3, Glue, Docker, CI/CD, GitHub Actions, Git, Databricks</t>
+          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, Databricks, PostgreSQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f396088cbf8cedc</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Redshift, CI/CD, Jenkins, Git, Redshift, Python</t>
+          <t>RAG, Cortex, Data Lake, AKS, CI/CD, Git, Snowflake, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b83410cfb11a99d</t>
+          <t>https://www.indeed.com/viewjob?jk=7bf2e42812735206</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, CI/CD, GitHub Actions, Git, MySQL, MongoDB, NoSQL, Power BI, SQL, R</t>
+          <t>RAG, Copilot, S3, Git, Databricks, PostgreSQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58f00f5a0707436</t>
+          <t>https://www.indeed.com/viewjob?jk=2770e8ca105cfd05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,99 +766,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Databricks, Kafka, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Glue, Git, Databricks, PySpark, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf29a6b43a49ae</t>
+          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Agentic Software Engineer</t>
+          <t>Consultant - Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Torq Consulting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27060d07882d0fbc</t>
+          <t>https://www.indeed.com/viewjob?jk=5246522f135f363a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Consultant - Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Evolve vacation rentals</t>
+          <t>Torq Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Data Lake, CI/CD, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47837312b0e5d7cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7b35fad850172c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer (Data Architecture)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,81 +867,81 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>Copilot, Glue, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42ac46bdb574412</t>
+          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Web Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ACT</t>
+          <t>Pelican Products, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iowa City, IA, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d2f27d51c055ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=8388fd80ca25899f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering MTS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1f235e7c67f5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=73f11a773e7e5f54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Test Engineer</t>
+          <t>AI Engineer, People Technology</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,357 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b2df47a2c7f568</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Python-AI Engineer Agentic Systems</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Citi</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Git, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c462696a046fe90</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer Full Stack / Backend II (Full-Time) - United States</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a887578c9e44d7e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Security Engineer III</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Aspirion</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c77964bcc3b4d3b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Supply Chain Operations</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5cfbc33620816a</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aebd55b3221a1a76</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>KLA</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Milpitas, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, PyTorch, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a55006fc9efc58</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Power Platform, Copilot Studio, Azure</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e841a5a1c02dc01</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>JLL</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=293d986f254547dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Rocket</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MI, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Git, Hadoop, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=546d4bc55a750071</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>SDET Web Automation</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da2a4ffcbfc48ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=c32a70f985dca743</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-26.xlsx
+++ b/daily_matches/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,242 +496,242 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5087fc206cc0738e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9ca78d46c32c41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Architect</t>
+          <t>AI Engineer (Python, Machine Learning, Generative AI/LLMs)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Modus Create</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, CI/CD, Git, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3282af658369b2af</t>
+          <t>https://www.indeed.com/viewjob?jk=2dcf5c5c1c2855a1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Software Engineer II, Fintech</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Quicksight</t>
+          <t>AI Engineer, RAG, Copilot, S3, Redshift, CI/CD, Terraform, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0e151be0bbb235</t>
+          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer II, Fintech</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Electric Power Engineers</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>AI Engineer, RAG, Copilot, S3, Redshift, CI/CD, Terraform, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3ddf4250ef85b5</t>
+          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data AI Engineer - Java</t>
+          <t>Senior Software Engineer (Solutions) - TypeScript/Node.js/React</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CNA Insurance</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, BigQuery, Data Lake, Dataflow, CI/CD, BigQuery, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874c68aa6c38b010</t>
+          <t>https://www.indeed.com/viewjob?jk=0494aa8c9d790ea1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>U.S based Senior AI Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, Databricks, PostgreSQL, NoSQL, Python</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Kafka, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a7e25c97039733</t>
+          <t>https://www.indeed.com/viewjob?jk=28370f7e43b9276b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Data Lake, AKS, CI/CD, Git, Snowflake, Tableau, Power BI, Python</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bf2e42812735206</t>
+          <t>https://www.indeed.com/viewjob?jk=82cbd1f5bd78afb0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Git, Databricks, PostgreSQL, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, Keras, NLTK, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2770e8ca105cfd05</t>
+          <t>https://www.indeed.com/viewjob?jk=736603db9af75528</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Glue, Git, Databricks, PySpark, Kafka, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, Keras, NLTK, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700aff8e79b7a5eb</t>
+          <t>https://www.indeed.com/viewjob?jk=1ddfff0d73adc542</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Consultant - Software Engineer</t>
+          <t>Research Scientist / Software Engineer, LLM/Agent Platform - TikTok - Content Ecology AI Innovation &amp; Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Torq Consulting</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, FAISS, TensorFlow, PyTorch, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5246522f135f363a</t>
+          <t>https://www.indeed.com/viewjob?jk=e4883cede1a1dfd7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Consultant - Software Engineer</t>
+          <t>Senior Go Lang Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Torq Consulting</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>RAG, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7b35fad850172c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b707da62cb9f27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Data Architecture)</t>
+          <t>Senior Go Lang Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copilot, Glue, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,112 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46aed55033a852ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Web Developer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Pelican Products, Inc.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Torrance, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8388fd80ca25899f</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineering MTS</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73f11a773e7e5f54</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AI Engineer, People Technology</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c32a70f985dca743</t>
+          <t>https://www.indeed.com/viewjob?jk=773420fec473c4e5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-26.xlsx
+++ b/daily_matches/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ProArch</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, SQL, R</t>
+          <t>RAG, AWS SageMaker, S3, Glue, Redshift, Synapse, Data Lake, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9ca78d46c32c41</t>
+          <t>https://www.indeed.com/viewjob?jk=08c354cd10dc0d65</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer (Python, Machine Learning, Generative AI/LLMs)</t>
+          <t>Senior Specialist - Data Sciences</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Jenkins, Git, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dcf5c5c1c2855a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f794d6e7bb8089a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II, Fintech</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>MetTel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, S3, Redshift, CI/CD, Terraform, Redshift, Python, SQL</t>
+          <t>RAG, Copilot, BigQuery, Data Lake, Kubernetes, CI/CD, Snowflake, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c724ec5809ede378</t>
+          <t>https://www.indeed.com/viewjob?jk=7cdad9aa5658efec</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II, Fintech</t>
+          <t>Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Castle Rock Associates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, S3, Redshift, CI/CD, Terraform, Redshift, Python, SQL</t>
+          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,49 +601,49 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ec45fe0952b39c</t>
+          <t>https://www.indeed.com/viewjob?jk=3538beb714b8a6c0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Solutions) - TypeScript/Node.js/React</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Jenkins, Git, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0494aa8c9d790ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0792fba749b538</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U.S based Senior AI Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,15 +653,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Kafka, Hadoop, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Docker, CI/CD, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28370f7e43b9276b</t>
+          <t>https://www.indeed.com/viewjob?jk=be46bc9a67f8e21e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed AI Engineer / Solutions Architect (GenAI, AWS)</t>
+          <t>Senior Analytics Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+          <t>RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82cbd1f5bd78afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=6da72b4f8dd2050c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, Keras, NLTK, Git, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Git, NoSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736603db9af75528</t>
+          <t>https://www.indeed.com/viewjob?jk=870a4881511329a2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI &amp; Process Automation Specialist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Yogurtland</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,122 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, Keras, NLTK, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Git, Power BI, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddfff0d73adc542</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Research Scientist / Software Engineer, LLM/Agent Platform - TikTok - Content Ecology AI Innovation &amp; Platform</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, FAISS, TensorFlow, PyTorch, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e4883cede1a1dfd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Go Lang Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b707da62cb9f27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Go Lang Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Menlo Park, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=773420fec473c4e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f10431b537fdd2</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-26.xlsx
+++ b/daily_matches/job_matches_2026-08-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ProArch</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, S3, Glue, Redshift, Synapse, Data Lake, Snowflake, Databricks, Redshift</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c354cd10dc0d65</t>
+          <t>https://www.indeed.com/viewjob?jk=124139dc71cb3de3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Sciences</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Jenkins, Git, MySQL, MongoDB</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f794d6e7bb8089a</t>
+          <t>https://www.indeed.com/viewjob?jk=909a1f6b26c17925</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MetTel</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Data Lake, Kubernetes, CI/CD, Snowflake, BigQuery, Kafka, Python</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cdad9aa5658efec</t>
+          <t>https://www.indeed.com/viewjob?jk=c93acac401ad3bbf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Security Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Castle Rock Associates</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3538beb714b8a6c0</t>
+          <t>https://www.indeed.com/viewjob?jk=94f4a28dfa9476bc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Jenkins, Git, MongoDB, Python, SQL, R</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0792fba749b538</t>
+          <t>https://www.indeed.com/viewjob?jk=13f55062141bc024</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Docker, CI/CD, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be46bc9a67f8e21e</t>
+          <t>https://www.indeed.com/viewjob?jk=93208e2f6926347a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Data Platform</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da72b4f8dd2050c</t>
+          <t>https://www.indeed.com/viewjob?jk=7eea24c2a0ab6c8d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Git, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,2772 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870a4881511329a2</t>
+          <t>https://www.indeed.com/viewjob?jk=1b928b70f880f43e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI &amp; Process Automation Specialist</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yogurtland</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Helena, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c53c3f82e674c498</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52c28366a273c1cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b120619fc2e804f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Annapolis, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9da89a063f9c8521</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Santa Fe, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd1b6aefc05efd92</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Concord, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b821791df6fb974a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e73a1e57486a0c1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a17a59c378aa6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Springfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ce6fa4c0175733b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2328e655f3e8d78f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a81d7d772ab85759</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>20</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=526ba6cf1cb5f265</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Frankfort, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1925f45d961a4413</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Charleston, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>20</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=345d49ceaf51b3dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Jefferson City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4237b23eb5e0e0e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Montpelier, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=342cda44215c91c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27914ea323041751</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fce442c2387b717</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27ca7d2c6b1b746c</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36418ba6cc0c14c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Salem, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af4943f5569a0767</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Carson City, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9b4f3ef2e79895a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b2d271a63d05bf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cheyenne, WY, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>20</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00aac80eaaee8a4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Montgomery, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a89e649b137768be</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Olympia, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>20</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38c7ac9df441601c</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f4418551c98d3ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f19d7d7cf4d3ecc</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Trenton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>20</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9041cb7d9adbbd88</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bismarck, ND, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9eb22c28a20aec81</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>20</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7a01a365ccb6479</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>20</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=197c01a921c0f589</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3fff2959c75f6c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>20</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d40d369719872875</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53a1b379b0810dfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>20</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b4bcbf3821afe5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>20</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32734f2534389aff</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D47" t="n">
+        <v>20</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2430a8d9cbfed099</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>20</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=026ee3ac609c3551</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>20</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=762089df3fb6872a</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Augusta, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>20</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d788e97a3bd89302</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>20</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60b50bb9dfbb5aa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>20</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f36a75009e4ba82</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Valsoft</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f71178b235857a8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, S3, MLflow, Kubernetes, Apache Airflow, Terraform, Kafka, Hadoop, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a001f2cdcb66bc68</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AI Engineer/Anthropic-Campus Hire - US West</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NewRocket</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d641b20a21dd61d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AI Engineer/Anthropic-Campus Hire - US West</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NewRocket</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95f9eff5d1f58ab6</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI Engineer/Anthropic-Campus Hire - US West</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NewRocket</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96336479aa6ca2ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Engineer/Anthropic-Campus Hire - US West</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NewRocket</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=925a82016166c525</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AI Engineer/Anthropic-Campus Hire - US West</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NewRocket</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Vista, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ae80d18ad38caaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Applied Science Data Frameworks</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, CI/CD, Databricks, Dask, Python</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bd749931cb478bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, CI/CD, Snowflake, BigQuery, Hadoop</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d1b15647f88acc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sr Data &amp; AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Grocery Outlet</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Emeryville, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, Data Lake, Kinesis, Snowflake, Databricks, Kafka, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60f0706c31a0334f</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SAVO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25ae2459a9a3dbd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ai Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ConsultBae</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Canada, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, CI/CD, Terraform, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd85c9b331ef9be0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, PostgreSQL, MySQL, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cc4691c730c638e</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Development Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>bp</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e24f70ff61678f2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, MongoDB, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64543ec5f02890f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, MongoDB, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15a494f407d22227</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, MongoDB, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2546a365f20e983</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, MongoDB, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7988a3ee97db7900</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Scientist, XGBoost, LightGBM, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3066fb4806ce93ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SAVO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Power BI, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, FastAPI, CI/CD, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a004d31a13a7a148</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Junior Data Migration Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4564d8d55c6a87e</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Jenkins, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a28485007e465c63</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Full Stack AEM Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afc836c36da3b044</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b00279eae7ec92e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c681a9056e23349f</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bbfa5155595ec72</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SHI International</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2af81e1348449422</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Grocery Outlet</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Emeryville, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, CI/CD, Kafka, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7bce2bfb23066e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Lennar</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75066f8919649116</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Analytics</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>AES Corporation</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f10431b537fdd2</t>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fbf73e2a2d7e581</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Analytics</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>AES Corporation</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66a5f3320c6af81a</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Analytics</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>AES Corporation</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Louisville, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a9f00ed4d637eba</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sr. Scientific Data Engineer, R&amp;D Data Platform</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Abbott Park, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, Glue, Athena, Git, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8280545268f9a67b</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=744d7c76f60ba3b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=494ed66beb3fab12</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Connected Vehicle Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Textron Specialized Vehicles</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Augusta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>S3, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfac0a590ec45dcb</t>
         </is>
       </c>
     </row>
